--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487663_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487663_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5671</v>
+        <v>1.9919</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4558</v>
+        <v>3.0168</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8887</v>
+        <v>-1.0249</v>
       </c>
       <c r="G2" t="n">
         <v>-1.9667</v>
@@ -610,13 +610,13 @@
         <v>3.6866</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0199</v>
+        <v>-1.5951</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1138</v>
+        <v>-0.5527</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9062</v>
+        <v>-1.0425</v>
       </c>
       <c r="V2" t="n">
         <v>4.0015</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7701</v>
+        <v>1.2612</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1734</v>
+        <v>1.4737</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4033</v>
+        <v>-0.2125</v>
       </c>
       <c r="G3" t="n">
         <v>0.1819</v>
@@ -688,13 +688,13 @@
         <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7701</v>
+        <v>-0.279</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2176</v>
+        <v>0.0827</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5525</v>
+        <v>-0.3617</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7696</v>
+        <v>0.5148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3367</v>
+        <v>0.1365</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4329</v>
+        <v>0.3783</v>
       </c>
       <c r="G4" t="n">
         <v>3.7164</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3517</v>
+        <v>0.097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3286</v>
+        <v>0.1284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0231</v>
+        <v>-0.0314</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.162</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.9655</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0273</v>
+        <v>0.4005</v>
       </c>
       <c r="G5" t="n">
         <v>-2.1761</v>
@@ -844,13 +844,13 @@
         <v>3.2985</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.456</v>
+        <v>-1.183</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1436</v>
+        <v>-0.2437</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3124</v>
+        <v>-0.9393</v>
       </c>
       <c r="V5" t="n">
         <v>0.6597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1496</v>
+        <v>-0.8132</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9573</v>
+        <v>-0.7571</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1923</v>
+        <v>-0.056</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0185</v>
@@ -922,13 +922,13 @@
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2191</v>
+        <v>-0.8827</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8557</v>
+        <v>-0.7195</v>
       </c>
       <c r="V6" t="n">
         <v>0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7968</v>
+        <v>-1.606</v>
       </c>
       <c r="E7" t="n">
         <v>-1.4436</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3532</v>
+        <v>-0.1624</v>
       </c>
       <c r="G7" t="n">
         <v>0.3108</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2434</v>
+        <v>-1.0526</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3634</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.88</v>
+        <v>-0.6892</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2821</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9921</v>
+        <v>-3.1556</v>
       </c>
       <c r="E8" t="n">
         <v>-0.9473</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0447</v>
+        <v>-2.2082</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2795</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2066</v>
+        <v>-0.3701</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3028</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="V8" t="n">
         <v>-1.506</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9109</v>
+        <v>-4.962</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9477</v>
+        <v>-1.0898</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0367</v>
+        <v>-3.8722</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4835</v>
+        <v>-1.0916</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.0196</v>
+        <v>-1.8051</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4638</v>
+        <v>0.7135</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4274</v>
+        <v>1.0979</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.174</v>
+        <v>1.174</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2535</v>
+        <v>-0.0762</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.056</v>
+        <v>-2.1895</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8457</v>
+        <v>-2.9791</v>
       </c>
       <c r="O9" t="n">
         <v>0.7897</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1045</v>
+        <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2248</v>
+        <v>-0.7823</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3903</v>
+        <v>-0.2473</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1655</v>
+        <v>-0.535</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8462</v>
+        <v>-2.1179</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8462</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9313</v>
+        <v>-5.4326</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9502</v>
+        <v>-5.3876</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9812</v>
+        <v>-0.045</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0916</v>
+        <v>-4.4835</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8051</v>
+        <v>-4.0196</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7135</v>
+        <v>-0.4638</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0979</v>
+        <v>-2.4274</v>
       </c>
       <c r="K10" t="n">
-        <v>1.174</v>
+        <v>-1.174</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0762</v>
+        <v>-1.2535</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1895</v>
+        <v>-2.056</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.9791</v>
+        <v>-2.8457</v>
       </c>
       <c r="O10" t="n">
         <v>0.7897</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>3.1045</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7517</v>
+        <v>-0.2969</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1077</v>
+        <v>-0.0497</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.644</v>
+        <v>-0.2473</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1179</v>
+        <v>-0.8462</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1179</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7564</v>
+        <v>-5.5323</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0975</v>
+        <v>-4.0369</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6589</v>
+        <v>-1.4954</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0549</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0612</v>
+        <v>-1.8371</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8962</v>
+        <v>-0.8356</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1651</v>
+        <v>-1.0015</v>
       </c>
       <c r="V11" t="n">
         <v>0.9418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.6311</v>
+        <v>-8.298</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2131</v>
+        <v>-5.1525</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4181</v>
+        <v>-3.1455</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8609</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9762</v>
+        <v>-1.6431</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9567</v>
+        <v>-0.8962</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0195</v>
+        <v>-0.7469</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2716</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.8994</v>
+        <v>-26.5968</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.4562</v>
+        <v>-15.1533</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.4435</v>
+        <v>-11.4433</v>
       </c>
       <c r="G13" t="n">
         <v>-13.7226</v>
@@ -1438,10 +1438,10 @@
         <v>-14.4177</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6951999999999995</v>
+        <v>0.6951999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>3.327900000000001</v>
+        <v>3.3279</v>
       </c>
       <c r="K13" t="n">
         <v>6.525199999999999</v>
@@ -1468,16 +1468,16 @@
         <v>18.4331</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.1277</v>
+        <v>-9.8249</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7463</v>
+        <v>-3.4435</v>
       </c>
       <c r="U13" t="n">
         <v>-6.3816</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1387</v>
+        <v>-0.1386999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>6.306</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.501300000000001</v>
+        <v>10.4595</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7941</v>
+        <v>6.2946</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7072</v>
+        <v>4.1649</v>
       </c>
       <c r="G14" t="n">
         <v>6.3272</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1025</v>
+        <v>1.0607</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0595</v>
+        <v>0.441</v>
       </c>
       <c r="U14" t="n">
-        <v>0.162</v>
+        <v>0.6197</v>
       </c>
       <c r="V14" t="n">
         <v>4.2358</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9673</v>
+        <v>7.4095</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5128</v>
+        <v>4.0123</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4544</v>
+        <v>3.3971</v>
       </c>
       <c r="G15" t="n">
         <v>5.2844</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1889</v>
+        <v>1.631</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2752</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9137</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2821</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0306</v>
+        <v>4.3745</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9494</v>
+        <v>1.3293</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0813</v>
+        <v>3.0453</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1747</v>
+        <v>0.9271</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2381</v>
+        <v>3.1315</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0634</v>
+        <v>-2.2044</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5714</v>
+        <v>0.7609</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1576</v>
+        <v>2.6817</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5861</v>
+        <v>-1.9208</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3967</v>
+        <v>0.1662</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9195</v>
+        <v>0.4498</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5227000000000001</v>
+        <v>-0.2836</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0321</v>
+        <v>1.7011</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3481</v>
+        <v>0.7624</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.9388</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7039</v>
+        <v>3.3027</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6286</v>
+        <v>0.2487</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0753</v>
+        <v>3.054</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9271</v>
+        <v>0.1747</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1315</v>
+        <v>0.2381</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2044</v>
+        <v>-0.0634</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7609</v>
+        <v>0.5714</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6817</v>
+        <v>1.1576</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9208</v>
+        <v>-0.5861</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1662</v>
+        <v>-0.3967</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4498</v>
+        <v>-0.9195</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2836</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0305</v>
+        <v>1.3041</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0617</v>
+        <v>0.6474</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9688</v>
+        <v>0.6567</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>F. JIMENO GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4964</v>
+        <v>2.5486</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5682</v>
+        <v>1.9143</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9282</v>
+        <v>0.6343</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2725</v>
+        <v>0.3543</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8216</v>
+        <v>-0.4927</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4509</v>
+        <v>0.847</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1234</v>
+        <v>0.6324</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7837</v>
+        <v>-0.6261</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3397</v>
+        <v>1.2585</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1491</v>
+        <v>-0.2781</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0379</v>
+        <v>0.1335</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1112</v>
+        <v>-0.4115</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.0747</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9105</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9897</v>
+        <v>0.1943</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0031</v>
+        <v>0.058</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9866</v>
+        <v>0.1363</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6015</v>
+        <v>1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5164</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0877</v>
+        <v>2.4787</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5263</v>
+        <v>1.9257</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5614</v>
+        <v>0.553</v>
       </c>
       <c r="G19" t="n">
         <v>2.2776</v>
@@ -1936,13 +1936,13 @@
         <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9459</v>
+        <v>1.3369</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4087</v>
+        <v>0.8081</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5373</v>
+        <v>0.5289</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9418</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. JIMENO GONZALEZ</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1665</v>
+        <v>2.4381</v>
       </c>
       <c r="E20" t="n">
-        <v>1.614</v>
+        <v>0.5672</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5526</v>
+        <v>1.8709</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3543</v>
+        <v>3.2725</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4927</v>
+        <v>1.8216</v>
       </c>
       <c r="I20" t="n">
-        <v>0.847</v>
+        <v>1.4509</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6324</v>
+        <v>3.1234</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6261</v>
+        <v>1.7837</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2585</v>
+        <v>1.3397</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2781</v>
+        <v>0.1491</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1335</v>
+        <v>0.0379</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4115</v>
+        <v>0.1112</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.0747</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>2.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1878</v>
+        <v>1.9313</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2423</v>
+        <v>1.0021</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0545</v>
+        <v>0.9292</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2239</v>
+        <v>-1.6015</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2239</v>
+        <v>0.5164</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1013</v>
+        <v>0.9169</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4316</v>
+        <v>0.2035</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3304</v>
+        <v>0.7135</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4809</v>
+        <v>0.3914</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1023</v>
+        <v>-0.3032</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5833</v>
+        <v>0.6946</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3835</v>
+        <v>1.1391</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0103</v>
+        <v>0.7003</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6267</v>
+        <v>0.4389</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8645</v>
+        <v>-0.7477</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9079</v>
+        <v>-1.0035</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9565</v>
+        <v>0.2558</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0076</v>
+        <v>0.7792</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.2285</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2057</v>
+        <v>0.5507</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4254</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1865</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3232</v>
+        <v>0.1891</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4972</v>
+        <v>0.3315</v>
       </c>
       <c r="F22" t="n">
-        <v>0.174</v>
+        <v>-0.1424</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3914</v>
+        <v>-0.4809</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3032</v>
+        <v>1.1023</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6946</v>
+        <v>-1.5833</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1391</v>
+        <v>1.3835</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7003</v>
+        <v>2.0103</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4389</v>
+        <v>-0.6267</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7477</v>
+        <v>-1.8645</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0035</v>
+        <v>-0.9079</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2558</v>
+        <v>-0.9565</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.461</v>
+        <v>1.0955</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4722</v>
+        <v>0.7018</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0112</v>
+        <v>0.3937</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>-0.4254</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1865</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.307</v>
+        <v>-1.376</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9653</v>
+        <v>-1.4648</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3417</v>
+        <v>0.0887</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6049</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4484</v>
+        <v>0.4825</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0595</v>
+        <v>0.441</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3889</v>
+        <v>0.0415</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5252</v>
+        <v>-3.84</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1189</v>
+        <v>-3.9187</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4063</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2007</v>
@@ -2326,13 +2326,13 @@
         <v>1.9403</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0722</v>
+        <v>0.6129</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3163</v>
+        <v>0.5165</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3885</v>
+        <v>0.0965</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.89960000000001</v>
+        <v>28.90160000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4436</v>
+        <v>11.44359999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>15.456</v>
+        <v>17.458</v>
       </c>
       <c r="G25" t="n">
         <v>13.7227</v>
@@ -2404,22 +2404,22 @@
         <v>21.3435</v>
       </c>
       <c r="S25" t="n">
-        <v>10.1278</v>
+        <v>12.1295</v>
       </c>
       <c r="T25" t="n">
-        <v>6.3815</v>
+        <v>6.381499999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>3.7464</v>
+        <v>5.7484</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1387000000000007</v>
+        <v>0.1387</v>
       </c>
       <c r="W25" t="n">
         <v>6.4447</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.306000000000001</v>
+        <v>-6.305999999999999</v>
       </c>
     </row>
   </sheetData>
